--- a/Optima_Capture_Bot.xlsx
+++ b/Optima_Capture_Bot.xlsx
@@ -86,7 +86,47 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="11">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -526,7 +566,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-29 19:23:00</t>
+          <t>2026-06-02 14:46:29</t>
         </is>
       </c>
     </row>
@@ -556,7 +596,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-29 19:23:20</t>
+          <t>2026-06-02 14:46:29</t>
         </is>
       </c>
     </row>
@@ -586,7 +626,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-29 19:23:43</t>
+          <t>2026-06-02 14:46:30</t>
         </is>
       </c>
     </row>
@@ -616,7 +656,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-29 19:24:06</t>
+          <t>2026-06-02 14:46:30</t>
         </is>
       </c>
     </row>
@@ -646,7 +686,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-29 19:24:28</t>
+          <t>2026-06-02 14:46:30</t>
         </is>
       </c>
     </row>
@@ -676,7 +716,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-30 10:27:41</t>
+          <t>2026-06-02 14:46:30</t>
         </is>
       </c>
     </row>
@@ -706,7 +746,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-30 10:27:57</t>
+          <t>2026-06-02 14:46:30</t>
         </is>
       </c>
     </row>
@@ -736,7 +776,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-30 10:57:41</t>
+          <t>2026-06-02 14:46:31</t>
         </is>
       </c>
     </row>
@@ -766,7 +806,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-30 10:58:20</t>
+          <t>2026-06-02 14:46:31</t>
         </is>
       </c>
     </row>
@@ -796,7 +836,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-30 11:51:30</t>
+          <t>2026-06-02 14:46:31</t>
         </is>
       </c>
     </row>
@@ -826,7 +866,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-30 11:52:01</t>
+          <t>2026-06-02 14:46:31</t>
         </is>
       </c>
     </row>
@@ -856,7 +896,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-30 12:22:20</t>
+          <t>2026-06-02 14:46:31</t>
         </is>
       </c>
     </row>
@@ -886,7 +926,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-30 12:22:49</t>
+          <t>2026-06-02 14:46:31</t>
         </is>
       </c>
     </row>
@@ -916,7 +956,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-30 12:23:21</t>
+          <t>2026-06-02 14:46:32</t>
         </is>
       </c>
     </row>
@@ -946,7 +986,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-30 12:23:52</t>
+          <t>2026-06-02 14:46:32</t>
         </is>
       </c>
     </row>
@@ -976,7 +1016,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-30 12:24:22</t>
+          <t>2026-06-02 14:46:32</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1046,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-30 12:24:54</t>
+          <t>2026-06-02 14:46:32</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1076,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-30 12:25:24</t>
+          <t>2026-06-02 14:46:32</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1106,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-30 12:25:55</t>
+          <t>2026-06-02 14:46:32</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1136,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-30 12:26:24</t>
+          <t>2026-06-02 14:46:32</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1166,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-30 12:26:54</t>
+          <t>2026-06-02 14:46:32</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1196,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-30 12:27:27</t>
+          <t>2026-06-02 14:46:33</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1226,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-30 12:27:58</t>
+          <t>2026-06-02 14:46:33</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1256,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-30 12:28:30</t>
+          <t>2026-06-02 14:46:33</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1286,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-30 12:29:01</t>
+          <t>2026-06-02 14:46:33</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1316,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-30 12:29:32</t>
+          <t>2026-06-02 14:46:33</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1346,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-30 12:30:03</t>
+          <t>2026-06-02 14:46:33</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1376,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-30 12:30:34</t>
+          <t>2026-06-02 14:46:33</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1406,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-30 13:16:48</t>
+          <t>2026-06-02 14:46:34</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1436,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-30 13:17:17</t>
+          <t>2026-06-02 14:46:34</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1466,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-30 13:17:49</t>
+          <t>2026-06-02 14:46:34</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1496,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-30 13:18:18</t>
+          <t>2026-06-02 14:46:34</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1526,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-30 13:18:48</t>
+          <t>2026-06-02 14:46:34</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1556,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-30 13:19:20</t>
+          <t>2026-06-02 14:46:34</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1586,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-30 13:19:47</t>
+          <t>2026-06-02 14:46:34</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1616,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-30 13:20:18</t>
+          <t>2026-06-02 14:46:35</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1646,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-30 13:20:48</t>
+          <t>2026-06-02 14:46:35</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1676,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-30 13:21:19</t>
+          <t>2026-06-02 14:46:35</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1706,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-30 13:21:49</t>
+          <t>2026-06-02 14:46:35</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1736,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-30 13:22:21</t>
+          <t>2026-06-02 14:46:35</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1766,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-30 13:22:51</t>
+          <t>2026-06-02 14:46:35</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1796,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-30 13:23:23</t>
+          <t>2026-06-02 14:46:35</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1826,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-30 13:23:54</t>
+          <t>2026-06-02 14:46:36</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1856,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-30 13:24:23</t>
+          <t>2026-06-02 14:46:36</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1886,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-30 13:24:55</t>
+          <t>2026-06-02 14:46:36</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1916,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-30 13:25:27</t>
+          <t>2026-06-02 14:46:36</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1946,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-30 13:25:56</t>
+          <t>2026-06-02 14:46:36</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1976,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-30 13:26:25</t>
+          <t>2026-06-02 14:46:36</t>
         </is>
       </c>
     </row>
@@ -1966,7 +2006,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-30 13:33:36</t>
+          <t>2026-06-02 14:46:36</t>
         </is>
       </c>
     </row>
@@ -1996,7 +2036,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-30 13:34:08</t>
+          <t>2026-06-02 14:46:37</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2066,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-30 13:34:43</t>
+          <t>2026-06-02 14:46:37</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2096,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-30 13:35:14</t>
+          <t>2026-06-02 14:46:37</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2126,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-30 13:35:45</t>
+          <t>2026-06-02 14:46:37</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2156,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-30 13:36:15</t>
+          <t>2026-06-02 14:46:37</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2186,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-30 13:36:47</t>
+          <t>2026-06-02 14:46:37</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2216,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-30 13:37:18</t>
+          <t>2026-06-02 14:46:37</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2246,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-01 17:17:44</t>
+          <t>2026-06-02 14:46:38</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2276,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-01 17:18:04</t>
+          <t>2026-06-02 14:46:38</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2306,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-01 17:18:24</t>
+          <t>2026-06-02 14:46:38</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2336,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-01 17:18:44</t>
+          <t>2026-06-02 14:46:38</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2366,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-01 17:19:05</t>
+          <t>2026-06-02 14:46:38</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2396,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-01 17:19:24</t>
+          <t>2026-06-02 14:46:38</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2426,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-01 17:19:43</t>
+          <t>2026-06-02 14:46:38</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2456,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-01 17:20:03</t>
+          <t>2026-06-02 14:46:39</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2486,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-01 18:49:54</t>
+          <t>2026-06-02 14:46:39</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2516,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-01 18:50:21</t>
+          <t>2026-06-02 14:46:39</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2546,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-01 19:03:51</t>
+          <t>2026-06-02 14:46:39</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2576,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-01 19:04:19</t>
+          <t>2026-06-02 14:46:39</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2606,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-01 19:27:04</t>
+          <t>2026-06-02 14:46:39</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2636,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-01 19:27:29</t>
+          <t>2026-06-02 14:46:39</t>
         </is>
       </c>
     </row>
@@ -2626,7 +2666,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-01 19:27:57</t>
+          <t>2026-06-02 14:46:40</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2696,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-01 19:28:24</t>
+          <t>2026-06-02 14:46:40</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2726,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-01 19:28:51</t>
+          <t>2026-06-02 14:46:40</t>
         </is>
       </c>
     </row>
@@ -2716,354 +2756,3459 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-01 19:29:17</t>
+          <t>2026-06-02 14:46:40</t>
         </is>
       </c>
     </row>
     <row r="76" ht="14.25" customHeight="1">
-      <c r="B76" s="4" t="n"/>
+      <c r="A76" s="6" t="n">
+        <v>1271</v>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>70027100569764831</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Lote_1</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:40</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
-      <c r="B77" s="4" t="n"/>
+      <c r="A77" s="6" t="n">
+        <v>1272</v>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>70027100579764842</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Lote_1</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:40</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
-      <c r="B78" s="4" t="n"/>
+      <c r="A78" s="6" t="n">
+        <v>1273</v>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>70027100589764853</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Lote_1</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:40</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="14.25" customHeight="1">
-      <c r="B79" s="4" t="n"/>
+      <c r="A79" s="6" t="n">
+        <v>1274</v>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>70027100599764864</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Lote_1</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:41</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="14.25" customHeight="1">
-      <c r="B80" s="4" t="n"/>
+      <c r="A80" s="6" t="n">
+        <v>1275</v>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>70027100619764886</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Lote_1</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:41</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
-      <c r="B81" s="4" t="n"/>
+      <c r="A81" s="6" t="n">
+        <v>1276</v>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>70027100639764811</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Lote_1</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:41</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
-      <c r="B82" s="4" t="n"/>
+      <c r="A82" s="6" t="n">
+        <v>1277</v>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>70027100649764822</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Lote_1</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:41</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="14.25" customHeight="1">
-      <c r="B83" s="4" t="n"/>
+      <c r="A83" s="6" t="n">
+        <v>1278</v>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>70027100659764833</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Lote_1</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:41</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="14.25" customHeight="1">
-      <c r="B84" s="4" t="n"/>
+      <c r="A84" s="6" t="n">
+        <v>1279</v>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>70027100669764844</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Lote_1</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:41</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="14.25" customHeight="1">
-      <c r="B85" s="4" t="n"/>
+      <c r="A85" s="6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>70027100679764855</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Lote_1</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:41</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
-      <c r="B86" s="4" t="n"/>
+      <c r="A86" s="6" t="n">
+        <v>1281</v>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>70027100689764866</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Lote_1</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:42</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
-      <c r="B87" s="4" t="n"/>
+      <c r="A87" s="6" t="n">
+        <v>1282</v>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>70027100699764877</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Lote_1</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:42</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="14.25" customHeight="1">
-      <c r="B88" s="4" t="n"/>
+      <c r="A88" s="6" t="n">
+        <v>1283</v>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>70027100719764802</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Lote_1</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:42</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="14.25" customHeight="1">
-      <c r="B89" s="4" t="n"/>
+      <c r="A89" s="6" t="n">
+        <v>1284</v>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>70027100729764813</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Lote_1</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:42</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="14.25" customHeight="1">
-      <c r="B90" s="4" t="n"/>
+      <c r="A90" s="6" t="n">
+        <v>1285</v>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>70027100739764824</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Lote_1</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:42</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
-      <c r="B91" s="4" t="n"/>
+      <c r="A91" s="6" t="n">
+        <v>1286</v>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>70027100759764846</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Lote_1</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:42</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="14.25" customHeight="1">
-      <c r="B92" s="4" t="n"/>
+      <c r="A92" s="6" t="n">
+        <v>1287</v>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>70027100769764857</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Lote_1</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:42</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="14.25" customHeight="1">
-      <c r="B93" s="4" t="n"/>
+      <c r="A93" s="6" t="n">
+        <v>1288</v>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>70027100779764868</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Lote_1</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:43</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="14.25" customHeight="1">
-      <c r="B94" s="4" t="n"/>
+      <c r="A94" s="6" t="n">
+        <v>1289</v>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>70027100789764879</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Lote_1</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:43</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="14.25" customHeight="1">
-      <c r="B95" s="4" t="n"/>
+      <c r="A95" s="6" t="n">
+        <v>1290</v>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>70027102809764838</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Lote_1</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:43</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="14.25" customHeight="1">
-      <c r="B96" s="4" t="n"/>
+      <c r="A96" s="6" t="n">
+        <v>1291</v>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>70027102839764871</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Lote_1</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:43</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
-      <c r="B97" s="4" t="n"/>
+      <c r="A97" s="6" t="n">
+        <v>1292</v>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>70027102849764882</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Lote_1</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:43</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
-      <c r="B98" s="4" t="n"/>
+      <c r="A98" s="6" t="n">
+        <v>1293</v>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>70027102869764807</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Lote_1</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:43</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="14.25" customHeight="1">
-      <c r="B99" s="4" t="n"/>
+      <c r="A99" s="6" t="n">
+        <v>1294</v>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>70027102889764829</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Lote_1</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:43</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="14.25" customHeight="1">
-      <c r="B100" s="4" t="n"/>
+      <c r="A100" s="6" t="n">
+        <v>1295</v>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>70027102899764840</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Lote_1</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:43</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="14.25" customHeight="1">
-      <c r="B101" s="4" t="n"/>
+      <c r="A101" s="6" t="n">
+        <v>1296</v>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>70027102909764851</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Lote_1</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:44</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="14.25" customHeight="1">
-      <c r="B102" s="4" t="n"/>
+      <c r="A102" s="6" t="n">
+        <v>1297</v>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>70027102919764862</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:44</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
-      <c r="B103" s="4" t="n"/>
+      <c r="A103" s="6" t="n">
+        <v>1298</v>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>70027102939764884</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:44</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="14.25" customHeight="1">
-      <c r="B104" s="4" t="n"/>
+      <c r="A104" s="6" t="n">
+        <v>1299</v>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>70027102969764820</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:44</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="14.25" customHeight="1">
-      <c r="B105" s="4" t="n"/>
+      <c r="A105" s="6" t="n">
+        <v>1300</v>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>70027102979764831</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:44</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="14.25" customHeight="1">
-      <c r="B106" s="4" t="n"/>
+      <c r="A106" s="6" t="n">
+        <v>1301</v>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>70027102989764842</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:44</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="14.25" customHeight="1">
-      <c r="B107" s="4" t="n"/>
+      <c r="A107" s="6" t="n">
+        <v>1302</v>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>70027103009764848</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:44</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
-      <c r="B108" s="4" t="n"/>
+      <c r="A108" s="6" t="n">
+        <v>1303</v>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>70027103019764859</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:45</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
-      <c r="B109" s="4" t="n"/>
+      <c r="A109" s="6" t="n">
+        <v>1304</v>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>70027103039764881</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:45</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="14.25" customHeight="1">
-      <c r="B110" s="4" t="n"/>
+      <c r="A110" s="6" t="n">
+        <v>1305</v>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>70027103059764806</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:45</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="14.25" customHeight="1">
-      <c r="B111" s="4" t="n"/>
+      <c r="A111" s="6" t="n">
+        <v>1306</v>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>70027103069764817</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:45</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
-      <c r="B112" s="4" t="n"/>
+      <c r="A112" s="6" t="n">
+        <v>1307</v>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>70027103089764839</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:45</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="14.25" customHeight="1">
-      <c r="B113" s="4" t="n"/>
+      <c r="A113" s="6" t="n">
+        <v>1308</v>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>70027103099764850</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:45</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="14.25" customHeight="1">
-      <c r="B114" s="4" t="n"/>
+      <c r="A114" s="6" t="n">
+        <v>1309</v>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>70027103109764861</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:45</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="14.25" customHeight="1">
-      <c r="B115" s="4" t="n"/>
+      <c r="A115" s="6" t="n">
+        <v>1310</v>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>70027103129764883</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:46</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="14.25" customHeight="1">
-      <c r="B116" s="4" t="n"/>
+      <c r="A116" s="6" t="n">
+        <v>1311</v>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>70027103139764894</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:46</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
-      <c r="B117" s="4" t="n"/>
+      <c r="A117" s="6" t="n">
+        <v>1312</v>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>70027103159764819</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:46</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
-      <c r="B118" s="4" t="n"/>
+      <c r="A118" s="6" t="n">
+        <v>1313</v>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>70027103169764830</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:46</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="14.25" customHeight="1">
-      <c r="B119" s="4" t="n"/>
+      <c r="A119" s="6" t="n">
+        <v>1314</v>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>70027103179764841</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:46</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="14.25" customHeight="1">
-      <c r="B120" s="4" t="n"/>
+      <c r="A120" s="6" t="n">
+        <v>1315</v>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>70027103189764852</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:46</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="14.25" customHeight="1">
-      <c r="B121" s="4" t="n"/>
+      <c r="A121" s="6" t="n">
+        <v>1316</v>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>70027103199764863</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:46</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="14.25" customHeight="1">
-      <c r="B122" s="4" t="n"/>
+      <c r="A122" s="6" t="n">
+        <v>1317</v>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>70027103209764874</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:47</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="14.25" customHeight="1">
-      <c r="B123" s="4" t="n"/>
+      <c r="A123" s="6" t="n">
+        <v>1318</v>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>70027103219764885</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:47</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="14.25" customHeight="1">
-      <c r="B124" s="4" t="n"/>
+      <c r="A124" s="6" t="n">
+        <v>1319</v>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>70027103229764896</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:47</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="14.25" customHeight="1">
-      <c r="B125" s="4" t="n"/>
+      <c r="A125" s="6" t="n">
+        <v>1320</v>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>70027103239764810</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:47</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="14.25" customHeight="1">
-      <c r="B126" s="4" t="n"/>
+      <c r="A126" s="6" t="n">
+        <v>1321</v>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>70027103399764889</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:47</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
-      <c r="B127" s="4" t="n"/>
+      <c r="A127" s="6" t="n">
+        <v>1322</v>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>70027103529764838</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:47</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="14.25" customHeight="1">
-      <c r="B128" s="4" t="n"/>
+      <c r="A128" s="6" t="n">
+        <v>1323</v>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>70027103549764860</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:47</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="14.25" customHeight="1">
-      <c r="B129" s="4" t="n"/>
+      <c r="A129" s="6" t="n">
+        <v>1324</v>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>70027103559764871</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:48</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="14.25" customHeight="1">
-      <c r="B130" s="4" t="n"/>
+      <c r="A130" s="6" t="n">
+        <v>1325</v>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>70027103609764829</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:48</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="14.25" customHeight="1">
-      <c r="B131" s="4" t="n"/>
+      <c r="A131" s="6" t="n">
+        <v>1326</v>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>70027103619764840</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:48</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="14.25" customHeight="1">
-      <c r="B132" s="4" t="n"/>
+      <c r="A132" s="6" t="n">
+        <v>1327</v>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>70027103629764851</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:48</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="14.25" customHeight="1">
-      <c r="B133" s="4" t="n"/>
+      <c r="A133" s="6" t="n">
+        <v>1328</v>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>70027103639764862</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:48</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="14.25" customHeight="1">
-      <c r="B134" s="4" t="n"/>
+      <c r="A134" s="6" t="n">
+        <v>1329</v>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>70027103729764864</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:48</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="14.25" customHeight="1">
-      <c r="B135" s="4" t="n"/>
+      <c r="A135" s="6" t="n">
+        <v>1330</v>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>70027104029764887</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:48</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="14.25" customHeight="1">
-      <c r="B136" s="4" t="n"/>
+      <c r="A136" s="6" t="n">
+        <v>1331</v>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>70027104049764812</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:49</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="14.25" customHeight="1">
-      <c r="B137" s="4" t="n"/>
+      <c r="A137" s="6" t="n">
+        <v>1332</v>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>70027104059764823</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:49</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
-      <c r="B138" s="4" t="n"/>
+      <c r="A138" s="6" t="n">
+        <v>1333</v>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>70027104069764834</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:49</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="14.25" customHeight="1">
-      <c r="B139" s="4" t="n"/>
+      <c r="A139" s="6" t="n">
+        <v>1334</v>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>70027104079764845</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:49</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="14.25" customHeight="1">
-      <c r="B140" s="4" t="n"/>
+      <c r="A140" s="6" t="n">
+        <v>1335</v>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>70027104089764856</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:49</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="14.25" customHeight="1">
-      <c r="B141" s="4" t="n"/>
+      <c r="A141" s="6" t="n">
+        <v>1336</v>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>70027104109764878</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:49</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
-      <c r="B142" s="4" t="n"/>
+      <c r="A142" s="6" t="n">
+        <v>1337</v>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>70027104119764889</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:49</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
-      <c r="B143" s="4" t="n"/>
+      <c r="A143" s="6" t="n">
+        <v>1338</v>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>70027104149764825</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:49</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="14.25" customHeight="1">
-      <c r="B144" s="4" t="n"/>
+      <c r="A144" s="6" t="n">
+        <v>1339</v>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>70027104179764858</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:50</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="14.25" customHeight="1">
-      <c r="B145" s="4" t="n"/>
+      <c r="A145" s="6" t="n">
+        <v>1340</v>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>70027107639764833</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:50</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="14.25" customHeight="1">
-      <c r="B146" s="4" t="n"/>
+      <c r="A146" s="6" t="n">
+        <v>1341</v>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>70027107659764855</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:50</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
-      <c r="B147" s="4" t="n"/>
+      <c r="A147" s="6" t="n">
+        <v>1342</v>
+      </c>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>70027108119764860</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:50</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="14.25" customHeight="1">
-      <c r="B148" s="4" t="n"/>
+      <c r="A148" s="6" t="n">
+        <v>1343</v>
+      </c>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t>70027108149764893</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:50</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
-      <c r="B149" s="4" t="n"/>
+      <c r="A149" s="6" t="n">
+        <v>1344</v>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>70027108169764818</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:50</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="14.25" customHeight="1">
-      <c r="B150" s="4" t="n"/>
+      <c r="A150" s="6" t="n">
+        <v>1345</v>
+      </c>
+      <c r="B150" s="5" t="inlineStr">
+        <is>
+          <t>70027108179764829</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:50</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="14.25" customHeight="1">
-      <c r="B151" s="4" t="n"/>
+      <c r="A151" s="6" t="n">
+        <v>1346</v>
+      </c>
+      <c r="B151" s="5" t="inlineStr">
+        <is>
+          <t>70027108199764851</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:51</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="14.25" customHeight="1">
-      <c r="B152" s="4" t="n"/>
+      <c r="A152" s="6" t="n">
+        <v>1347</v>
+      </c>
+      <c r="B152" s="5" t="inlineStr">
+        <is>
+          <t>70027108209764862</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:51</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="14.25" customHeight="1">
-      <c r="B153" s="4" t="n"/>
+      <c r="A153" s="6" t="n">
+        <v>1348</v>
+      </c>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>70027108219764873</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:51</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="14.25" customHeight="1">
-      <c r="B154" s="4" t="n"/>
+      <c r="A154" s="6" t="n">
+        <v>1349</v>
+      </c>
+      <c r="B154" s="5" t="inlineStr">
+        <is>
+          <t>70027108229764884</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:46:51</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="14.25" customHeight="1">
-      <c r="B155" s="4" t="n"/>
+      <c r="A155" s="6" t="n">
+        <v>1350</v>
+      </c>
+      <c r="B155" s="5" t="inlineStr">
+        <is>
+          <t>70027108249764809</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-06-02 17:05:49</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
-      <c r="B156" s="4" t="n"/>
+      <c r="A156" s="6" t="n">
+        <v>1351</v>
+      </c>
+      <c r="B156" s="5" t="inlineStr">
+        <is>
+          <t>70027108279764842</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-06-02 17:06:16</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="14.25" customHeight="1">
-      <c r="B157" s="4" t="n"/>
+      <c r="A157" s="6" t="n">
+        <v>1352</v>
+      </c>
+      <c r="B157" s="5" t="inlineStr">
+        <is>
+          <t>70027108299764864</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-06-02 17:06:42</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
-      <c r="B158" s="4" t="n"/>
+      <c r="A158" s="6" t="n">
+        <v>1353</v>
+      </c>
+      <c r="B158" s="5" t="inlineStr">
+        <is>
+          <t>70027108319764886</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-06-02 17:07:10</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
-      <c r="B159" s="4" t="n"/>
+      <c r="A159" s="6" t="n">
+        <v>1354</v>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
+        <is>
+          <t>70027108349764822</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-06-02 17:07:38</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="14.25" customHeight="1">
-      <c r="B160" s="4" t="n"/>
+      <c r="A160" s="6" t="n">
+        <v>1355</v>
+      </c>
+      <c r="B160" s="5" t="inlineStr">
+        <is>
+          <t>70027108359764833</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-06-02 17:08:07</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
-      <c r="B161" s="4" t="n"/>
+      <c r="A161" s="6" t="n">
+        <v>1356</v>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
+        <is>
+          <t>70027108369764844</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-06-02 17:08:36</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
-      <c r="B162" s="4" t="n"/>
+      <c r="A162" s="6" t="n">
+        <v>1357</v>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
+        <is>
+          <t>70027108399764877</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-06-02 17:09:03</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
-      <c r="B163" s="4" t="n"/>
+      <c r="A163" s="6" t="n">
+        <v>1358</v>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
+        <is>
+          <t>70027108429764813</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-06-02 17:09:33</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="14.25" customHeight="1">
-      <c r="B164" s="4" t="n"/>
+      <c r="A164" s="6" t="n">
+        <v>1359</v>
+      </c>
+      <c r="B164" s="5" t="inlineStr">
+        <is>
+          <t>70027108449764835</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-06-02 17:10:00</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="14.25" customHeight="1">
-      <c r="B165" s="4" t="n"/>
+      <c r="A165" s="6" t="n">
+        <v>1360</v>
+      </c>
+      <c r="B165" s="5" t="inlineStr">
+        <is>
+          <t>70027108479764868</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-06-02 17:10:27</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
-      <c r="B166" s="4" t="n"/>
+      <c r="A166" s="6" t="n">
+        <v>1361</v>
+      </c>
+      <c r="B166" s="5" t="inlineStr">
+        <is>
+          <t>70027108509764804</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-06-02 17:10:55</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="14.25" customHeight="1">
-      <c r="B167" s="4" t="n"/>
+      <c r="A167" s="6" t="n">
+        <v>1362</v>
+      </c>
+      <c r="B167" s="5" t="inlineStr">
+        <is>
+          <t>70027108649764861</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-06-02 17:11:22</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="14.25" customHeight="1">
-      <c r="B168" s="4" t="n"/>
+      <c r="A168" s="6" t="n">
+        <v>1363</v>
+      </c>
+      <c r="B168" s="5" t="inlineStr">
+        <is>
+          <t>70027107619764811</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-06-02 17:11:48</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="14.25" customHeight="1">
-      <c r="B169" s="4" t="n"/>
+      <c r="A169" s="6" t="n">
+        <v>1364</v>
+      </c>
+      <c r="B169" s="5" t="inlineStr">
+        <is>
+          <t>70027108789764821</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-06-02 17:12:17</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="14.25" customHeight="1">
-      <c r="B170" s="4" t="n"/>
+      <c r="A170" s="6" t="n">
+        <v>1365</v>
+      </c>
+      <c r="B170" s="5" t="inlineStr">
+        <is>
+          <t>70027108819764854</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-06-02 17:12:46</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
-      <c r="B171" s="4" t="n"/>
+      <c r="A171" s="6" t="n">
+        <v>1366</v>
+      </c>
+      <c r="B171" s="5" t="inlineStr">
+        <is>
+          <t>70027108889764834</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-06-02 17:13:15</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="14.25" customHeight="1">
-      <c r="B172" s="4" t="n"/>
+      <c r="A172" s="6" t="n">
+        <v>1367</v>
+      </c>
+      <c r="B172" s="5" t="inlineStr">
+        <is>
+          <t>70027108899764845</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-06-02 17:13:44</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="14.25" customHeight="1">
-      <c r="B173" s="4" t="n"/>
+      <c r="A173" s="6" t="n">
+        <v>1368</v>
+      </c>
+      <c r="B173" s="5" t="inlineStr">
+        <is>
+          <t>70027109029764875</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-06-02 17:14:10</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="14.25" customHeight="1">
-      <c r="B174" s="4" t="n"/>
+      <c r="A174" s="6" t="n">
+        <v>1369</v>
+      </c>
+      <c r="B174" s="5" t="inlineStr">
+        <is>
+          <t>70027109049764897</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-06-02 17:14:38</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="14.25" customHeight="1">
-      <c r="B175" s="4" t="n"/>
+      <c r="A175" s="6" t="n">
+        <v>1370</v>
+      </c>
+      <c r="B175" s="5" t="inlineStr">
+        <is>
+          <t>70027109059764811</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-06-02 17:15:05</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
-      <c r="B176" s="4" t="n"/>
+      <c r="A176" s="6" t="n">
+        <v>1371</v>
+      </c>
+      <c r="B176" s="5" t="inlineStr">
+        <is>
+          <t>70027109069764822</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-06-02 18:21:32</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
-      <c r="B177" s="4" t="n"/>
+      <c r="A177" s="6" t="n">
+        <v>1372</v>
+      </c>
+      <c r="B177" s="5" t="inlineStr">
+        <is>
+          <t>70027109099764855</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-06-02 18:22:03</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="14.25" customHeight="1">
-      <c r="B178" s="4" t="n"/>
+      <c r="A178" s="6" t="n">
+        <v>1373</v>
+      </c>
+      <c r="B178" s="5" t="inlineStr">
+        <is>
+          <t>70027109119764877</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-06-02 18:22:35</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="14.25" customHeight="1">
-      <c r="B179" s="4" t="n"/>
+      <c r="A179" s="6" t="n">
+        <v>1374</v>
+      </c>
+      <c r="B179" s="5" t="inlineStr">
+        <is>
+          <t>70027109129764888</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-06-02 18:23:08</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="14.25" customHeight="1">
-      <c r="B180" s="4" t="n"/>
+      <c r="A180" s="6" t="n">
+        <v>1375</v>
+      </c>
+      <c r="B180" s="5" t="inlineStr">
+        <is>
+          <t>70027109169764835</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-06-02 18:23:40</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
-      <c r="B181" s="4" t="n"/>
+      <c r="A181" s="6" t="n">
+        <v>1376</v>
+      </c>
+      <c r="B181" s="5" t="inlineStr">
+        <is>
+          <t>70027109189764857</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-06-02 18:24:09</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
-      <c r="B182" s="4" t="n"/>
+      <c r="A182" s="6" t="n">
+        <v>1377</v>
+      </c>
+      <c r="B182" s="5" t="inlineStr">
+        <is>
+          <t>70027109219764890</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-06-02 18:24:40</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
-      <c r="B183" s="4" t="n"/>
+      <c r="A183" s="6" t="n">
+        <v>1378</v>
+      </c>
+      <c r="B183" s="5" t="inlineStr">
+        <is>
+          <t>70027109229764804</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-06-02 18:25:09</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
-      <c r="B184" s="4" t="n"/>
+      <c r="A184" s="6" t="n">
+        <v>1379</v>
+      </c>
+      <c r="B184" s="5" t="inlineStr">
+        <is>
+          <t>70027109239764815</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-06-02 18:25:42</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="14.25" customHeight="1">
-      <c r="B185" s="4" t="n"/>
+      <c r="A185" s="6" t="n">
+        <v>1380</v>
+      </c>
+      <c r="B185" s="5" t="inlineStr">
+        <is>
+          <t>70027109249764826</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-06-02 18:26:14</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="14.25" customHeight="1">
-      <c r="B186" s="4" t="n"/>
+      <c r="A186" s="6" t="n">
+        <v>1381</v>
+      </c>
+      <c r="B186" s="5" t="inlineStr">
+        <is>
+          <t>70027109269764848</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2026-06-02 18:26:45</t>
+        </is>
+      </c>
     </row>
     <row r="187" ht="14.25" customHeight="1">
-      <c r="B187" s="4" t="n"/>
+      <c r="A187" s="6" t="n">
+        <v>1382</v>
+      </c>
+      <c r="B187" s="5" t="inlineStr">
+        <is>
+          <t>70027109279764859</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2026-06-02 18:27:17</t>
+        </is>
+      </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
-      <c r="B188" s="4" t="n"/>
+      <c r="A188" s="6" t="n">
+        <v>1383</v>
+      </c>
+      <c r="B188" s="5" t="inlineStr">
+        <is>
+          <t>70027109289764870</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2026-06-02 18:29:18</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
-      <c r="B189" s="4" t="n"/>
+      <c r="A189" s="6" t="n">
+        <v>1384</v>
+      </c>
+      <c r="B189" s="5" t="inlineStr">
+        <is>
+          <t>70027109299764881</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>2026-06-02 18:29:49</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="14.25" customHeight="1">
-      <c r="B190" s="4" t="n"/>
+      <c r="A190" s="6" t="n">
+        <v>1385</v>
+      </c>
+      <c r="B190" s="5" t="inlineStr">
+        <is>
+          <t>70027109309764892</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Lote_2</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>2026-06-02 18:30:21</t>
+        </is>
+      </c>
     </row>
     <row r="191" ht="14.25" customHeight="1">
       <c r="B191" s="4" t="n"/>
@@ -3599,24 +6744,36 @@
     <row r="700" ht="14.25" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="B2:B29">
+    <cfRule type="duplicateValues" priority="11" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30:B49">
+    <cfRule type="duplicateValues" priority="10" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B50:B59">
+    <cfRule type="duplicateValues" priority="9" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B60:B65">
+    <cfRule type="duplicateValues" priority="8" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B66:B67">
     <cfRule type="duplicateValues" priority="7" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B30:B49">
+  <conditionalFormatting sqref="B68:B69">
     <cfRule type="duplicateValues" priority="6" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B50:B59">
+  <conditionalFormatting sqref="B70:B75">
     <cfRule type="duplicateValues" priority="5" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B60:B65">
+  <conditionalFormatting sqref="B76:B104">
     <cfRule type="duplicateValues" priority="4" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B66:B67">
+  <conditionalFormatting sqref="B105:B154">
     <cfRule type="duplicateValues" priority="3" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B68:B69">
+  <conditionalFormatting sqref="B155:B175">
     <cfRule type="duplicateValues" priority="2" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B70:B75">
+  <conditionalFormatting sqref="B176:B190">
     <cfRule type="duplicateValues" priority="1" dxfId="0"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Optima_Capture_Bot.xlsx
+++ b/Optima_Capture_Bot.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-120" windowWidth="23280" windowHeight="12480" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Control_Referencias" sheetId="1" state="visible" r:id="rId1"/>
@@ -80,7 +80,27 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="14">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -476,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J204"/>
+  <dimension ref="A1:J212"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="7.7109375" customWidth="1" min="1" max="1"/>
@@ -6634,14 +6654,246 @@
         </is>
       </c>
     </row>
-    <row r="205" ht="14.25" customHeight="1"/>
-    <row r="206" ht="14.25" customHeight="1"/>
-    <row r="207" ht="14.25" customHeight="1"/>
-    <row r="208" ht="14.25" customHeight="1"/>
-    <row r="209" ht="14.25" customHeight="1"/>
-    <row r="210" ht="14.25" customHeight="1"/>
-    <row r="211" ht="14.25" customHeight="1"/>
-    <row r="212" ht="14.25" customHeight="1"/>
+    <row r="205" ht="14.25" customHeight="1">
+      <c r="A205" s="5" t="n">
+        <v>1400</v>
+      </c>
+      <c r="B205" s="4" t="inlineStr">
+        <is>
+          <t>70027109589764812</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Lote_3</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>2026-06-03 08:22:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="14.25" customHeight="1">
+      <c r="A206" s="5" t="n">
+        <v>1401</v>
+      </c>
+      <c r="B206" s="4" t="inlineStr">
+        <is>
+          <t>70027109609764834</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Lote_3</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>2026-06-03 08:23:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="14.25" customHeight="1">
+      <c r="A207" s="5" t="n">
+        <v>1402</v>
+      </c>
+      <c r="B207" s="4" t="inlineStr">
+        <is>
+          <t>70027109619764845</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Lote_3</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>2026-06-03 08:23:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="14.25" customHeight="1">
+      <c r="A208" s="5" t="n">
+        <v>1403</v>
+      </c>
+      <c r="B208" s="4" t="inlineStr">
+        <is>
+          <t>70027109629764856</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Lote_3</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>2026-06-03 08:24:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="14.25" customHeight="1">
+      <c r="A209" s="5" t="n">
+        <v>1404</v>
+      </c>
+      <c r="B209" s="4" t="inlineStr">
+        <is>
+          <t>70027109649764878</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Lote_3</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>2026-06-03 08:24:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="14.25" customHeight="1">
+      <c r="A210" s="5" t="n">
+        <v>1405</v>
+      </c>
+      <c r="B210" s="4" t="inlineStr">
+        <is>
+          <t>70027109689764825</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Lote_3</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>2026-06-03 08:25:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="14.25" customHeight="1">
+      <c r="A211" s="5" t="n">
+        <v>1406</v>
+      </c>
+      <c r="B211" s="4" t="inlineStr">
+        <is>
+          <t>70027109739764880</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Lote_3</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>2026-06-03 08:28:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="14.25" customHeight="1">
+      <c r="A212" s="5" t="n">
+        <v>1407</v>
+      </c>
+      <c r="B212" s="4" t="inlineStr">
+        <is>
+          <t>70027109749764891</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Lote_3</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>2026-06-03 08:29:32</t>
+        </is>
+      </c>
+    </row>
     <row r="213" ht="14.25" customHeight="1"/>
     <row r="214" ht="14.25" customHeight="1"/>
     <row r="215" ht="14.25" customHeight="1"/>
@@ -7132,39 +7384,45 @@
     <row r="700" ht="14.25" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="B2:B29">
+    <cfRule type="duplicateValues" priority="14" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30:B49">
+    <cfRule type="duplicateValues" priority="13" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B50:B59">
     <cfRule type="duplicateValues" priority="12" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B30:B49">
+  <conditionalFormatting sqref="B60:B65">
     <cfRule type="duplicateValues" priority="11" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B50:B59">
+  <conditionalFormatting sqref="B66:B67">
     <cfRule type="duplicateValues" priority="10" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B60:B65">
+  <conditionalFormatting sqref="B68:B69">
     <cfRule type="duplicateValues" priority="9" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B66:B67">
+  <conditionalFormatting sqref="B70:B75">
     <cfRule type="duplicateValues" priority="8" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B68:B69">
+  <conditionalFormatting sqref="B76:B104">
     <cfRule type="duplicateValues" priority="7" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B70:B75">
+  <conditionalFormatting sqref="B105:B154">
     <cfRule type="duplicateValues" priority="6" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B76:B104">
+  <conditionalFormatting sqref="B155:B175">
     <cfRule type="duplicateValues" priority="5" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B105:B154">
+  <conditionalFormatting sqref="B176:B190">
     <cfRule type="duplicateValues" priority="4" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B155:B175">
+  <conditionalFormatting sqref="B191:B204">
     <cfRule type="duplicateValues" priority="3" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B176:B190">
+  <conditionalFormatting sqref="B205:B210">
     <cfRule type="duplicateValues" priority="2" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B191:B204">
+  <conditionalFormatting sqref="B211:B212">
     <cfRule type="duplicateValues" priority="1" dxfId="0"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Optima_Capture_Bot.xlsx
+++ b/Optima_Capture_Bot.xlsx
@@ -80,7 +80,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="15">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -496,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J212"/>
+  <dimension ref="A1:J214"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="7.7109375" customWidth="1" min="1" max="1"/>
@@ -6894,8 +6904,66 @@
         </is>
       </c>
     </row>
-    <row r="213" ht="14.25" customHeight="1"/>
-    <row r="214" ht="14.25" customHeight="1"/>
+    <row r="213" ht="14.25" customHeight="1">
+      <c r="A213" s="5" t="n">
+        <v>1408</v>
+      </c>
+      <c r="B213" s="4" t="inlineStr">
+        <is>
+          <t>70027109759764805</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Lote_3</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:11:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="14.25" customHeight="1">
+      <c r="A214" s="5" t="n">
+        <v>1409</v>
+      </c>
+      <c r="B214" s="4" t="inlineStr">
+        <is>
+          <t>70027109769764816</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>CIN010904D31</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>OK-GENERADA</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Lote_3</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:11:34</t>
+        </is>
+      </c>
+    </row>
     <row r="215" ht="14.25" customHeight="1"/>
     <row r="216" ht="14.25" customHeight="1"/>
     <row r="217" ht="14.25" customHeight="1"/>
@@ -7384,45 +7452,48 @@
     <row r="700" ht="14.25" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="B2:B29">
+    <cfRule type="duplicateValues" priority="15" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30:B49">
     <cfRule type="duplicateValues" priority="14" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B30:B49">
+  <conditionalFormatting sqref="B50:B59">
     <cfRule type="duplicateValues" priority="13" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B50:B59">
+  <conditionalFormatting sqref="B60:B65">
     <cfRule type="duplicateValues" priority="12" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B60:B65">
+  <conditionalFormatting sqref="B66:B67">
     <cfRule type="duplicateValues" priority="11" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B66:B67">
+  <conditionalFormatting sqref="B68:B69">
     <cfRule type="duplicateValues" priority="10" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B68:B69">
+  <conditionalFormatting sqref="B70:B75">
     <cfRule type="duplicateValues" priority="9" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B70:B75">
+  <conditionalFormatting sqref="B76:B104">
     <cfRule type="duplicateValues" priority="8" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B76:B104">
+  <conditionalFormatting sqref="B105:B154">
     <cfRule type="duplicateValues" priority="7" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B105:B154">
+  <conditionalFormatting sqref="B155:B175">
     <cfRule type="duplicateValues" priority="6" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B155:B175">
+  <conditionalFormatting sqref="B176:B190">
     <cfRule type="duplicateValues" priority="5" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B176:B190">
+  <conditionalFormatting sqref="B191:B204">
     <cfRule type="duplicateValues" priority="4" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B191:B204">
+  <conditionalFormatting sqref="B205:B210">
     <cfRule type="duplicateValues" priority="3" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B205:B210">
+  <conditionalFormatting sqref="B211:B212">
     <cfRule type="duplicateValues" priority="2" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B211:B212">
+  <conditionalFormatting sqref="B213:B214">
     <cfRule type="duplicateValues" priority="1" dxfId="0"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
